--- a/base_history_metriques_sgd_train_val.xlsx
+++ b/base_history_metriques_sgd_train_val.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/725bbd4577e01318/Desktop/MASTER_IA_DIT/DEVOIR_DEEP_LEARNING/cnn-catsdogs-DrameSekou/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="34" documentId="11_2B59D2BFD370DC5B09E1D8F050A9A8765295F836" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05A8A19E-1873-4364-B98D-209126628E4C}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="11_2B59D2BFD370DC5B09E1D8F050A9A8765295F836" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6759BD9B-4DA3-4ED0-B8A7-97C8C2067812}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -72,12 +72,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -92,8 +98,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -109,10 +116,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -400,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.90625" bestFit="1" customWidth="1"/>
@@ -410,7 +413,7 @@
     <col min="8" max="8" width="11.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>7</v>
       </c>
@@ -436,7 +439,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -461,8 +464,12 @@
       <c r="H2">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="K2">
+        <f>MAX(E2:E11)</f>
+        <v>0.69511111111111112</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -488,7 +495,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -514,7 +521,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -540,7 +547,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -566,7 +573,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -592,7 +599,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -618,33 +625,33 @@
         <v>1E-4</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A9">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="1">
         <v>0.58017925527360703</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="1">
         <v>0.5731401171684265</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="1">
         <v>0.68894444444444447</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="1">
         <v>0.69511111111111112</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="1">
         <v>0.68846153846153846</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>0.71472937000887315</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>1E-4</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -670,7 +677,7 @@
         <v>1E-4</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>

--- a/base_history_metriques_sgd_train_val.xlsx
+++ b/base_history_metriques_sgd_train_val.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/725bbd4577e01318/Desktop/MASTER_IA_DIT/DEVOIR_DEEP_LEARNING/cnn-catsdogs-DrameSekou/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="11_2B59D2BFD370DC5B09E1D8F050A9A8765295F836" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6759BD9B-4DA3-4ED0-B8A7-97C8C2067812}"/>
+  <xr:revisionPtr revIDLastSave="37" documentId="11_2B59D2BFD370DC5B09E1D8F050A9A8765295F836" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0EBA929E-5BA9-4AE9-AE64-DFE2B2381D74}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.90625" bestFit="1" customWidth="1"/>
@@ -413,7 +413,7 @@
     <col min="8" max="8" width="11.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>7</v>
       </c>
@@ -439,7 +439,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -464,12 +464,8 @@
       <c r="H2">
         <v>0.01</v>
       </c>
-      <c r="K2">
-        <f>MAX(E2:E11)</f>
-        <v>0.69511111111111112</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -495,7 +491,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -521,7 +517,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -547,7 +543,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -573,7 +569,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -599,7 +595,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -625,7 +621,7 @@
         <v>1E-4</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -651,7 +647,7 @@
         <v>1E-4</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -677,7 +673,7 @@
         <v>1E-4</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
